--- a/original-input-data/mvv_gtfs_2037/Infrastructure_measures.xlsx
+++ b/original-input-data/mvv_gtfs_2037/Infrastructure_measures.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DavidBerling\Masterarbeit Lokal\WP2\Matsim-example-project-TU-Kurs\original-input-data\mvv_gtfs_2037\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8C73816-95A4-4AC3-B445-83A7E97B397C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A85952E1-3C3F-4B1C-832D-3032A38B1162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-6983" yWindow="-16297" windowWidth="28995" windowHeight="15675" xr2:uid="{C9EB77A7-838A-4CDA-9FC2-6F0F3DBDABA8}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="184">
   <si>
     <t>Definition BAU and FT:
 - Im BAU 2040 werden nur Maßnahmen berücksichtigt, deren Umsetzung bis 2040 bereits unabhängig von einer Olympiabewerbung hinreichend gesichert oder sehr plausibel ist.
@@ -573,6 +573,69 @@
   </si>
   <si>
     <t>Implementation follows the two-line operating concept of the U11 feasibility study. Both lines are generated as separate bidirectional GTFS routes</t>
+  </si>
+  <si>
+    <t>https://www.bahnausbau-muenchen.de/projekt.html?PID=108</t>
+  </si>
+  <si>
+    <t>S2</t>
+  </si>
+  <si>
+    <t>https://www.bahnausbau-muenchen.de/projekt.html?PID=42</t>
+  </si>
+  <si>
+    <t>https://www.bahnausbau-muenchen.de/regionalzughalt-poccistrasse.html</t>
+  </si>
+  <si>
+    <t>https://www.bahnausbau-muenchen.de/projekt.html?PID=5</t>
+  </si>
+  <si>
+    <t>Laim - Berduxstraße - Obermenzing</t>
+  </si>
+  <si>
+    <t>E 28.a BY; E 28.b BY; N 28.a BY; N 28.b BY; E 56 BY; N 56 BY</t>
+  </si>
+  <si>
+    <t>München Hbf – Poccistraße – München Ost; München Ost – Poccistraße – München Hbf</t>
+  </si>
+  <si>
+    <t>Existing GTFS 2037 timetable and frequencies are retained; Poccistraße is added to matching trips that traverse the München Hbf–München Ost corridor</t>
+  </si>
+  <si>
+    <t>Trips of the listed routes that do not traverse the München Hbf–München Ost corridor remain unchanged</t>
+  </si>
+  <si>
+    <t>Model assumption: all GTFS 2037 regional-train trips assigned to the Rosenheim or Mühldorf corridors and actually running between München Hbf and München Ost receive the new stop. Dwell time and additional running time are derived from comparable regional stops</t>
+  </si>
+  <si>
+    <t>S20; western S-Bahn services during disruptions</t>
+  </si>
+  <si>
+    <t>Existing regular routes retained; diversion and turning movements via Heimeranplatz are not simulated</t>
+  </si>
+  <si>
+    <t>No regular-service frequency change; existing GTFS 2037 timetable retained</t>
+  </si>
+  <si>
+    <t>Not applicable</t>
+  </si>
+  <si>
+    <t>No published change to the regular-day service pattern was identified. The measure primarily improves operational resilience during disruptions. Because the simulation represents a normal operating day without disruptions, no separate GTFS modification is implemented</t>
+  </si>
+  <si>
+    <t>Existing GTFS 2037 timetable retained; the stop is added to regular S2 trips. No additional departures are generated</t>
+  </si>
+  <si>
+    <t>Express S-Bahn services from Altomünster and Petershausen do not serve Berduxstraße</t>
+  </si>
+  <si>
+    <t>https://www.stmb.bayern.de/assets/stmi/vum/schiene/220519_machbarkeitsstudie_bericht_u06_final.pdf</t>
+  </si>
+  <si>
+    <t>Dwell time and additional running time are derived from comparable S-Bahn stops. The builder must distinguish regular S2 trips from express services</t>
+  </si>
+  <si>
+    <t>S20</t>
   </si>
 </sst>
 </file>
@@ -736,11 +799,6 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{61883FC4-1D17-4081-8945-EF8683794370}" name="Tabelle4" displayName="Tabelle4" ref="A4:P31" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A4:P31" xr:uid="{61883FC4-1D17-4081-8945-EF8683794370}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="nein"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="6">
       <filters>
         <filter val="ja"/>
@@ -1367,7 +1425,7 @@
       </c>
       <c r="L12" s="7"/>
     </row>
-    <row r="13" spans="1:18" hidden="1">
+    <row r="13" spans="1:18">
       <c r="B13" t="s">
         <v>88</v>
       </c>
@@ -1396,7 +1454,25 @@
         <v>89</v>
       </c>
       <c r="L13" t="s">
-        <v>134</v>
+        <v>165</v>
+      </c>
+      <c r="M13" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="N13" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="O13" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="P13" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>166</v>
+      </c>
+      <c r="R13" s="10" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1529,7 +1605,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="17" spans="2:18" hidden="1">
+    <row r="17" spans="2:18">
       <c r="B17" t="s">
         <v>81</v>
       </c>
@@ -1561,13 +1637,16 @@
         <v>134</v>
       </c>
     </row>
-    <row r="18" spans="2:18" hidden="1">
+    <row r="18" spans="2:18">
       <c r="B18" t="s">
         <v>83</v>
       </c>
       <c r="C18" t="s">
         <v>56</v>
       </c>
+      <c r="D18" s="10" t="s">
+        <v>183</v>
+      </c>
       <c r="E18" t="s">
         <v>74</v>
       </c>
@@ -1590,16 +1669,37 @@
         <v>84</v>
       </c>
       <c r="L18" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="19" spans="2:18" hidden="1">
+        <v>167</v>
+      </c>
+      <c r="M18" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="N18" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="O18" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="P18" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>167</v>
+      </c>
+      <c r="R18" s="10" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18">
       <c r="B19" t="s">
         <v>86</v>
       </c>
       <c r="C19" t="s">
         <v>56</v>
       </c>
+      <c r="D19" s="10" t="s">
+        <v>164</v>
+      </c>
       <c r="E19" t="s">
         <v>26</v>
       </c>
@@ -1619,7 +1719,25 @@
         <v>114</v>
       </c>
       <c r="L19" t="s">
-        <v>134</v>
+        <v>163</v>
+      </c>
+      <c r="M19" t="s">
+        <v>164</v>
+      </c>
+      <c r="N19" t="s">
+        <v>168</v>
+      </c>
+      <c r="O19" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="P19" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q19" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="R19" s="13" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="20" spans="2:18">
@@ -1690,7 +1808,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="22" spans="2:18" hidden="1">
+    <row r="22" spans="2:18">
       <c r="B22" t="s">
         <v>87</v>
       </c>
@@ -2026,7 +2144,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="31" spans="2:18" hidden="1">
+    <row r="31" spans="2:18">
       <c r="B31" t="s">
         <v>85</v>
       </c>
@@ -2065,10 +2183,11 @@
     <hyperlink ref="Q30" r:id="rId2" xr:uid="{BE22F3F0-2846-435C-B6CA-0BD8493B6880}"/>
     <hyperlink ref="Q29" r:id="rId3" xr:uid="{80A311A9-14ED-4AD4-8FFC-1270B33C2666}"/>
     <hyperlink ref="Q14" r:id="rId4" xr:uid="{5CE7C215-8E78-48EA-A2DF-1275BB4C83E4}"/>
+    <hyperlink ref="Q19" r:id="rId5" xr:uid="{D235CEED-9DC3-4E86-B456-9A68D7BB8D65}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>
--- a/original-input-data/mvv_gtfs_2037/Infrastructure_measures.xlsx
+++ b/original-input-data/mvv_gtfs_2037/Infrastructure_measures.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DavidBerling\Masterarbeit Lokal\WP2\Matsim-example-project-TU-Kurs\original-input-data\mvv_gtfs_2037\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A85952E1-3C3F-4B1C-832D-3032A38B1162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7412925D-FBA9-4B4A-89A2-D5446DBC4B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-6983" yWindow="-16297" windowWidth="28995" windowHeight="15675" xr2:uid="{C9EB77A7-838A-4CDA-9FC2-6F0F3DBDABA8}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="194">
   <si>
     <t>Definition BAU and FT:
 - Im BAU 2040 werden nur Maßnahmen berücksichtigt, deren Umsetzung bis 2040 bereits unabhängig von einer Olympiabewerbung hinreichend gesichert oder sehr plausibel ist.
@@ -636,6 +636,36 @@
   </si>
   <si>
     <t>S20</t>
+  </si>
+  <si>
+    <t>population_2040.xml; home and work activities</t>
+  </si>
+  <si>
+    <t>Centroid proxy (WGS84): 48.142233, 11.657852; transform to EPSG:31468 before implementation</t>
+  </si>
+  <si>
+    <t>Target assumption: 3,500 residents and 1,167 jobs; 5% sample: relocate 175 persons by home location and 58 work activities</t>
+  </si>
+  <si>
+    <t>No new persons are generated. Total population, activity times, plan structure and existing mode choices remain unchanged</t>
+  </si>
+  <si>
+    <t>https://stadt.muenchen.de/dam/jcr:7b868e98-b9f0-4310-ac7c-32d1c4b526d6/PraesentationNordosten.pdf</t>
+  </si>
+  <si>
+    <t>The permanent post-Games land-use mix has not yet been officially defined. Therefore, the accommodation capacity of 3,500 media professionals is used as a proxy for permanent residents. The job target is derived from the MNO-wide ratio of one job per three residents. The centroid is a manually derived model proxy. Selected locations are relocated deterministically using a fixed random seed</t>
+  </si>
+  <si>
+    <t>Centroid proxy (WGS84): 48.153739, 11.658821; transform to EPSG:31468 before implementation</t>
+  </si>
+  <si>
+    <t>Target: 10,500 residents and 3,500 jobs; 5% sample: relocate 525 persons by home location and 175 work activities</t>
+  </si>
+  <si>
+    <t>No new persons are generated. Total population, activity times, plan structure and existing mode choices remain unchanged.</t>
+  </si>
+  <si>
+    <t>The centroid is a model proxy manually derived from the official planning map, not an officially defined site centre. The residential target follows the published estimate of approximately 4,000 dwellings and 10,500 residents. The job target is derived from the MNO-wide ratio of 10,000 jobs to 30,000 residents. Selected locations are relocated deterministically using a fixed random seed.</t>
   </si>
 </sst>
 </file>
@@ -798,19 +828,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{61883FC4-1D17-4081-8945-EF8683794370}" name="Tabelle4" displayName="Tabelle4" ref="A4:P31" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A4:P31" xr:uid="{61883FC4-1D17-4081-8945-EF8683794370}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="ja"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="7">
-      <filters>
-        <filter val="nein"/>
-        <filter val="teilweise"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A4:P31" xr:uid="{61883FC4-1D17-4081-8945-EF8683794370}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:K31">
     <sortCondition ref="C4:C31"/>
   </sortState>
@@ -1345,7 +1363,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="14.4" hidden="1" customHeight="1">
+    <row r="10" spans="1:18" ht="14.4" customHeight="1">
       <c r="B10" t="s">
         <v>38</v>
       </c>
@@ -1371,7 +1389,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="14.4" hidden="1" customHeight="1">
+    <row r="11" spans="1:18" ht="14.4" customHeight="1">
       <c r="B11" t="s">
         <v>41</v>
       </c>
@@ -1398,7 +1416,7 @@
       </c>
       <c r="L11" s="7"/>
     </row>
-    <row r="12" spans="1:18" ht="14.4" hidden="1" customHeight="1">
+    <row r="12" spans="1:18" ht="14.4" customHeight="1">
       <c r="B12" t="s">
         <v>44</v>
       </c>
@@ -1573,7 +1591,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="16" spans="1:18" hidden="1">
+    <row r="16" spans="1:18">
       <c r="B16" t="s">
         <v>79</v>
       </c>
@@ -1770,8 +1788,23 @@
       <c r="L20" t="s">
         <v>136</v>
       </c>
-      <c r="M20" t="s">
-        <v>134</v>
+      <c r="M20" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="N20" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="O20" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="P20" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>188</v>
+      </c>
+      <c r="R20" s="13" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="2:18">
@@ -1804,8 +1837,23 @@
       <c r="L21" t="s">
         <v>136</v>
       </c>
-      <c r="M21" t="s">
-        <v>134</v>
+      <c r="M21" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="N21" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="O21" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="P21" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>188</v>
+      </c>
+      <c r="R21" s="13" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="2:18">
@@ -1837,7 +1885,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="23" spans="2:18" hidden="1">
+    <row r="23" spans="2:18">
       <c r="B23" t="s">
         <v>71</v>
       </c>
@@ -1869,7 +1917,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="24" spans="2:18" hidden="1">
+    <row r="24" spans="2:18">
       <c r="B24" t="s">
         <v>75</v>
       </c>
@@ -1901,7 +1949,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="2:18" hidden="1">
+    <row r="25" spans="2:18">
       <c r="B25" t="s">
         <v>77</v>
       </c>
@@ -1933,7 +1981,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="26" spans="2:18" hidden="1">
+    <row r="26" spans="2:18">
       <c r="B26" t="s">
         <v>18</v>
       </c>
@@ -1968,7 +2016,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="27" spans="2:18" hidden="1">
+    <row r="27" spans="2:18">
       <c r="B27" t="s">
         <v>24</v>
       </c>
@@ -2003,7 +2051,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="28" spans="2:18" hidden="1">
+    <row r="28" spans="2:18">
       <c r="B28" t="s">
         <v>27</v>
       </c>

--- a/original-input-data/mvv_gtfs_2037/Infrastructure_measures.xlsx
+++ b/original-input-data/mvv_gtfs_2037/Infrastructure_measures.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DavidBerling\Masterarbeit Lokal\WP2\Matsim-example-project-TU-Kurs\original-input-data\mvv_gtfs_2037\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7412925D-FBA9-4B4A-89A2-D5446DBC4B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188707BC-C75F-4078-8D7E-B7CC85ACC55B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-6983" yWindow="-16297" windowWidth="28995" windowHeight="15675" xr2:uid="{C9EB77A7-838A-4CDA-9FC2-6F0F3DBDABA8}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="195">
   <si>
     <t>Definition BAU and FT:
 - Im BAU 2040 werden nur Maßnahmen berücksichtigt, deren Umsetzung bis 2040 bereits unabhängig von einer Olympiabewerbung hinreichend gesichert oder sehr plausibel ist.
@@ -666,6 +666,9 @@
   </si>
   <si>
     <t>The centroid is a model proxy manually derived from the official planning map, not an officially defined site centre. The residential target follows the published estimate of approximately 4,000 dwellings and 10,500 residents. The job target is derived from the MNO-wide ratio of 10,000 jobs to 30,000 residents. Selected locations are relocated deterministically using a fixed random seed.</t>
+  </si>
+  <si>
+    <t>nicht berücksichtigen</t>
   </si>
 </sst>
 </file>
@@ -1876,7 +1879,7 @@
         <v>33</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>107</v>
+        <v>194</v>
       </c>
       <c r="J22" s="10" t="s">
         <v>117</v>
@@ -1884,6 +1887,7 @@
       <c r="L22" t="s">
         <v>134</v>
       </c>
+      <c r="R22" s="13"/>
     </row>
     <row r="23" spans="2:18">
       <c r="B23" t="s">

--- a/original-input-data/mvv_gtfs_2037/Infrastructure_measures.xlsx
+++ b/original-input-data/mvv_gtfs_2037/Infrastructure_measures.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DavidBerling\Masterarbeit Lokal\WP2\Matsim-example-project-TU-Kurs\original-input-data\mvv_gtfs_2037\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188707BC-C75F-4078-8D7E-B7CC85ACC55B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E078EFA-D45E-40DF-B97D-3AC5F358BD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-6983" yWindow="-16297" windowWidth="28995" windowHeight="15675" xr2:uid="{C9EB77A7-838A-4CDA-9FC2-6F0F3DBDABA8}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="200">
   <si>
     <t>Definition BAU and FT:
 - Im BAU 2040 werden nur Maßnahmen berücksichtigt, deren Umsetzung bis 2040 bereits unabhängig von einer Olympiabewerbung hinreichend gesichert oder sehr plausibel ist.
@@ -669,6 +669,21 @@
   </si>
   <si>
     <t>nicht berücksichtigen</t>
+  </si>
+  <si>
+    <t>Fast Track road network (network-with-pt.xml.gz); car mode</t>
+  </si>
+  <si>
+    <t>Herzog-Wilhelm-Straße: Sendlinger-Tor-Platz – Josephspitalstraße; complete Kreuzstraße</t>
+  </si>
+  <si>
+    <t>Not applicable – no timetable change. In Fast Track, car is removed from 11 Herzog-Wilhelm-Straße links, 1 Kreuzstraße link and technical boundary connector 126449; BAU remains unchanged</t>
+  </si>
+  <si>
+    <t>No PT stops or services are changed. The existing northern pedestrian section and adjacent streets such as Sonnenstraße, Sendlinger-Tor-Platz and Josephspitalstraße remain unchanged</t>
+  </si>
+  <si>
+    <t>Only the car restriction is represented. Pedestrian amenity, greening, deliveries, emergency and resident access, taxis, bicycles and implementation phasing are not modelled. Link 126449 is removed from the car network only as a technical boundary connector and does not extend the planned pedestrian area. Population and activities remain unchanged.</t>
   </si>
 </sst>
 </file>
@@ -1260,8 +1275,23 @@
       <c r="L6" t="s">
         <v>136</v>
       </c>
-      <c r="M6" t="s">
-        <v>134</v>
+      <c r="M6" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="N6" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="O6" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="P6" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q6" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="R6" s="13" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:18">

--- a/original-input-data/mvv_gtfs_2037/Infrastructure_measures.xlsx
+++ b/original-input-data/mvv_gtfs_2037/Infrastructure_measures.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DavidBerling\Masterarbeit Lokal\WP2\Matsim-example-project-TU-Kurs\original-input-data\mvv_gtfs_2037\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E078EFA-D45E-40DF-B97D-3AC5F358BD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8178535A-C300-4B41-8969-EABDD920BDA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-6983" yWindow="-16297" windowWidth="28995" windowHeight="15675" xr2:uid="{C9EB77A7-838A-4CDA-9FC2-6F0F3DBDABA8}"/>
+    <workbookView xWindow="-156" yWindow="-156" windowWidth="23352" windowHeight="12552" xr2:uid="{C9EB77A7-838A-4CDA-9FC2-6F0F3DBDABA8}"/>
   </bookViews>
   <sheets>
     <sheet name="Maßnahmen" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="202">
   <si>
     <t>Definition BAU and FT:
 - Im BAU 2040 werden nur Maßnahmen berücksichtigt, deren Umsetzung bis 2040 bereits unabhängig von einer Olympiabewerbung hinreichend gesichert oder sehr plausibel ist.
@@ -50,9 +50,6 @@
     <t>SUMP und seine 16 teilstrategien, mobilitätsstrategie 2035</t>
   </si>
   <si>
-    <t>measure_id</t>
-  </si>
-  <si>
     <t>measure_name</t>
   </si>
   <si>
@@ -72,9 +69,6 @@
   </si>
   <si>
     <t>included_fast_track_2040</t>
-  </si>
-  <si>
-    <t>eindeutige ID</t>
   </si>
   <si>
     <t>Name der Maßnahme</t>
@@ -684,6 +678,18 @@
   </si>
   <si>
     <t>Only the car restriction is represented. Pedestrian amenity, greening, deliveries, emergency and resident access, taxis, bicycles and implementation phasing are not modelled. Link 126449 is removed from the car network only as a technical boundary connector and does not extend the planned pedestrian area. Population and activities remain unchanged.</t>
+  </si>
+  <si>
+    <t>implemented</t>
+  </si>
+  <si>
+    <t>yes/no</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -846,12 +852,18 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{61883FC4-1D17-4081-8945-EF8683794370}" name="Tabelle4" displayName="Tabelle4" ref="A4:P31" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A4:P31" xr:uid="{61883FC4-1D17-4081-8945-EF8683794370}"/>
+  <autoFilter ref="A4:P31" xr:uid="{61883FC4-1D17-4081-8945-EF8683794370}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="yes"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:K31">
     <sortCondition ref="C4:C31"/>
   </sortState>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{D649CFB5-9DC9-4B17-995F-C0733BCC98A3}" name="eindeutige ID"/>
+    <tableColumn id="1" xr3:uid="{D649CFB5-9DC9-4B17-995F-C0733BCC98A3}" name="yes/no"/>
     <tableColumn id="2" xr3:uid="{000D3030-1293-44F4-9642-BAB2780CF35C}" name="Name der Maßnahme"/>
     <tableColumn id="3" xr3:uid="{7630E8E2-234E-45F1-8C88-21E64D01477E}" name="U-Bahn, S-Bahn, Tram, Bus, Rad, Straße"/>
     <tableColumn id="4" xr3:uid="{CAA074B5-97EF-4EA3-9DD7-C0A0C420821F}" name="Nr. der PT Linie"/>
@@ -1107,1155 +1119,1236 @@
     </row>
     <row r="3" spans="1:18" s="4" customFormat="1">
       <c r="A3" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>6</v>
-      </c>
       <c r="L3" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="M3" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="O3" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="P3" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="Q3" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="R3" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:18" s="6" customFormat="1" ht="53.7" customHeight="1">
       <c r="A4" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="E4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="K4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="L4" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>96</v>
-      </c>
       <c r="M4" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="N4" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="N4" s="5" t="s">
-        <v>137</v>
-      </c>
       <c r="O4" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="P4" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="P4" s="14" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
+    </row>
+    <row r="5" spans="1:18" hidden="1">
+      <c r="A5" t="s">
+        <v>200</v>
+      </c>
       <c r="B5" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>59</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>61</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="M5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:18">
+      <c r="A6" t="s">
+        <v>201</v>
+      </c>
       <c r="B6" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>68</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>70</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L6" t="s">
-        <v>136</v>
-      </c>
-      <c r="M6" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="M6" t="s">
+        <v>193</v>
+      </c>
+      <c r="N6" t="s">
+        <v>194</v>
+      </c>
+      <c r="O6" t="s">
         <v>195</v>
       </c>
-      <c r="N6" s="13" t="s">
+      <c r="P6" t="s">
         <v>196</v>
       </c>
-      <c r="O6" s="13" t="s">
+      <c r="Q6" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="R6" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="P6" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q6" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="R6" s="13" t="s">
-        <v>199</v>
-      </c>
     </row>
     <row r="7" spans="1:18">
+      <c r="A7" t="s">
+        <v>201</v>
+      </c>
       <c r="B7" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>62</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>64</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I7" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="J7" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="J7" s="10" t="s">
-        <v>105</v>
-      </c>
       <c r="K7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="M7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" hidden="1">
+      <c r="A8" t="s">
+        <v>200</v>
+      </c>
       <c r="B8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>46</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>48</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="M8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" hidden="1">
+      <c r="A9" t="s">
+        <v>200</v>
+      </c>
       <c r="B9" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>65</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>67</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G9" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="K9" t="s">
+        <v>64</v>
+      </c>
+      <c r="L9" t="s">
+        <v>134</v>
+      </c>
+      <c r="M9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="14.4" hidden="1" customHeight="1">
+      <c r="A10" t="s">
+        <v>200</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" t="s">
         <v>37</v>
       </c>
-      <c r="H9" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" s="10" t="s">
+    </row>
+    <row r="11" spans="1:18" ht="14.4" hidden="1" customHeight="1">
+      <c r="A11" t="s">
+        <v>200</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="L11" s="7"/>
+    </row>
+    <row r="12" spans="1:18" ht="14.4" hidden="1" customHeight="1">
+      <c r="A12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L12" s="7"/>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" t="s">
+        <v>201</v>
+      </c>
+      <c r="B13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="J13" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="J9" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="K9" t="s">
-        <v>66</v>
-      </c>
-      <c r="L9" t="s">
-        <v>136</v>
-      </c>
-      <c r="M9" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="14.4" customHeight="1">
-      <c r="B10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10" t="s">
-        <v>33</v>
-      </c>
-      <c r="K10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="14.4" customHeight="1">
-      <c r="B11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>33</v>
-      </c>
-      <c r="H11" t="s">
-        <v>33</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="L11" s="7"/>
-    </row>
-    <row r="12" spans="1:18" ht="14.4" customHeight="1">
-      <c r="B12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12" t="s">
-        <v>33</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="L12" s="7"/>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="B13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" t="s">
-        <v>33</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>108</v>
-      </c>
       <c r="K13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L13" t="s">
-        <v>165</v>
-      </c>
-      <c r="M13" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="M13" t="s">
+        <v>167</v>
+      </c>
+      <c r="N13" t="s">
+        <v>168</v>
+      </c>
+      <c r="O13" t="s">
         <v>169</v>
       </c>
-      <c r="N13" s="10" t="s">
+      <c r="P13" t="s">
         <v>170</v>
       </c>
-      <c r="O13" s="13" t="s">
+      <c r="Q13" t="s">
+        <v>164</v>
+      </c>
+      <c r="R13" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="P13" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>166</v>
-      </c>
-      <c r="R13" s="10" t="s">
-        <v>173</v>
-      </c>
     </row>
     <row r="14" spans="1:18">
+      <c r="A14" t="s">
+        <v>201</v>
+      </c>
       <c r="B14" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>54</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>56</v>
       </c>
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I14" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="J14" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="J14" s="10" t="s">
-        <v>109</v>
-      </c>
       <c r="K14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L14" t="s">
+        <v>134</v>
+      </c>
+      <c r="M14" t="s">
+        <v>156</v>
+      </c>
+      <c r="N14" t="s">
+        <v>157</v>
+      </c>
+      <c r="O14" t="s">
+        <v>158</v>
+      </c>
+      <c r="P14" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q14" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="R14" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" hidden="1">
+      <c r="A15" t="s">
+        <v>200</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L14" t="s">
-        <v>136</v>
-      </c>
-      <c r="M14" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="N14" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="O14" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="P14" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q14" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="R14" s="10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="B15" s="8" t="s">
-        <v>57</v>
-      </c>
       <c r="C15" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J15" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="K15" t="s">
+        <v>56</v>
+      </c>
+      <c r="L15" t="s">
+        <v>134</v>
+      </c>
+      <c r="M15" t="s">
+        <v>152</v>
+      </c>
+      <c r="N15" t="s">
+        <v>89</v>
+      </c>
+      <c r="O15" t="s">
+        <v>153</v>
+      </c>
+      <c r="P15" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>141</v>
+      </c>
+      <c r="R15" s="13" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" t="s">
+        <v>201</v>
+      </c>
+      <c r="B16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="K16" t="s">
+        <v>78</v>
+      </c>
+      <c r="L16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" hidden="1">
+      <c r="A17" t="s">
+        <v>200</v>
+      </c>
+      <c r="B17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="J17" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="K15" t="s">
-        <v>58</v>
-      </c>
-      <c r="L15" t="s">
-        <v>136</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="O15" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="P15" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>143</v>
-      </c>
-      <c r="R15" s="13" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" t="s">
-        <v>74</v>
-      </c>
-      <c r="F16" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" t="s">
-        <v>37</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J16" s="10" t="s">
+      <c r="K17" t="s">
+        <v>80</v>
+      </c>
+      <c r="L17" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" hidden="1">
+      <c r="A18" t="s">
+        <v>200</v>
+      </c>
+      <c r="B18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="E18" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="J18" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="K16" t="s">
-        <v>80</v>
-      </c>
-      <c r="L16" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="17" spans="2:18">
-      <c r="B17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" t="s">
-        <v>56</v>
-      </c>
-      <c r="E17" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" t="s">
-        <v>33</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="J17" s="10" t="s">
+      <c r="K18" t="s">
+        <v>82</v>
+      </c>
+      <c r="L18" t="s">
+        <v>165</v>
+      </c>
+      <c r="M18" t="s">
+        <v>172</v>
+      </c>
+      <c r="N18" t="s">
+        <v>173</v>
+      </c>
+      <c r="O18" t="s">
+        <v>174</v>
+      </c>
+      <c r="P18" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>165</v>
+      </c>
+      <c r="R18" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="A19" t="s">
+        <v>201</v>
+      </c>
+      <c r="B19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="E19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="J19" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="K17" t="s">
-        <v>82</v>
-      </c>
-      <c r="L17" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="18" spans="2:18">
-      <c r="B18" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="E18" t="s">
-        <v>74</v>
-      </c>
-      <c r="F18" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18" t="s">
-        <v>33</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="K18" t="s">
-        <v>84</v>
-      </c>
-      <c r="L18" t="s">
-        <v>167</v>
-      </c>
-      <c r="M18" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="N18" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="O18" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="P18" s="13" t="s">
+      <c r="L19" t="s">
+        <v>161</v>
+      </c>
+      <c r="M19" t="s">
+        <v>162</v>
+      </c>
+      <c r="N19" t="s">
+        <v>166</v>
+      </c>
+      <c r="O19" t="s">
         <v>177</v>
       </c>
-      <c r="Q18" t="s">
-        <v>167</v>
-      </c>
-      <c r="R18" s="10" t="s">
+      <c r="P19" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="19" spans="2:18">
-      <c r="B19" t="s">
-        <v>86</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="E19" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19" t="s">
-        <v>33</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="L19" t="s">
-        <v>163</v>
-      </c>
-      <c r="M19" t="s">
-        <v>164</v>
-      </c>
-      <c r="N19" t="s">
-        <v>168</v>
-      </c>
-      <c r="O19" s="13" t="s">
+      <c r="Q19" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="P19" s="13" t="s">
+      <c r="R19" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="Q19" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="R19" s="13" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="20" spans="2:18">
+    </row>
+    <row r="20" spans="1:18">
+      <c r="A20" t="s">
+        <v>201</v>
+      </c>
       <c r="B20" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>49</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>51</v>
       </c>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L20" t="s">
+        <v>134</v>
+      </c>
+      <c r="M20" t="s">
+        <v>182</v>
+      </c>
+      <c r="N20" t="s">
+        <v>188</v>
+      </c>
+      <c r="O20" t="s">
+        <v>189</v>
+      </c>
+      <c r="P20" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>186</v>
+      </c>
+      <c r="R20" s="13" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21" t="s">
+        <v>201</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="L20" t="s">
-        <v>136</v>
-      </c>
-      <c r="M20" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="N20" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="O20" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="P20" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>188</v>
-      </c>
-      <c r="R20" s="13" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="21" spans="2:18">
-      <c r="B21" s="8" t="s">
-        <v>52</v>
-      </c>
       <c r="C21" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
       <c r="F21" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="K21" t="s">
+        <v>51</v>
+      </c>
+      <c r="L21" t="s">
+        <v>134</v>
+      </c>
+      <c r="M21" t="s">
+        <v>182</v>
+      </c>
+      <c r="N21" t="s">
+        <v>183</v>
+      </c>
+      <c r="O21" t="s">
+        <v>184</v>
+      </c>
+      <c r="P21" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>186</v>
+      </c>
+      <c r="R21" s="13" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" hidden="1">
+      <c r="A22" t="s">
+        <v>200</v>
+      </c>
+      <c r="B22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" t="s">
+        <v>72</v>
+      </c>
+      <c r="F22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" t="s">
+        <v>21</v>
+      </c>
+      <c r="H22" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="L22" t="s">
+        <v>132</v>
+      </c>
+      <c r="R22" s="13"/>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23" t="s">
+        <v>201</v>
+      </c>
+      <c r="B23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23" t="s">
+        <v>35</v>
+      </c>
+      <c r="H23" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="K23" t="s">
+        <v>70</v>
+      </c>
+      <c r="L23" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="A24" t="s">
+        <v>201</v>
+      </c>
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" t="s">
+        <v>72</v>
+      </c>
+      <c r="F24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="K24" t="s">
+        <v>74</v>
+      </c>
+      <c r="L24" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="A25" t="s">
+        <v>201</v>
+      </c>
+      <c r="B25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" t="s">
+        <v>71</v>
+      </c>
+      <c r="E25" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="K25" t="s">
+        <v>76</v>
+      </c>
+      <c r="L25" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="A26" t="s">
+        <v>201</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="K26" t="s">
+        <v>18</v>
+      </c>
+      <c r="L26" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="A27" t="s">
+        <v>201</v>
+      </c>
+      <c r="B27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" t="s">
+        <v>24</v>
+      </c>
+      <c r="F27" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="A28" t="s">
+        <v>201</v>
+      </c>
+      <c r="B28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" t="s">
+        <v>20</v>
+      </c>
+      <c r="F28" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" t="s">
+        <v>21</v>
+      </c>
+      <c r="H28" t="s">
+        <v>35</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="K28" t="s">
+        <v>27</v>
+      </c>
+      <c r="L28" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="A29" t="s">
+        <v>201</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="K29" t="s">
+        <v>30</v>
+      </c>
+      <c r="L29" t="s">
+        <v>139</v>
+      </c>
+      <c r="M29" t="s">
+        <v>29</v>
+      </c>
+      <c r="N29" t="s">
+        <v>142</v>
+      </c>
+      <c r="O29" t="s">
+        <v>143</v>
+      </c>
+      <c r="P29" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q29" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="R29" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
+      <c r="A30" t="s">
+        <v>201</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G21" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="H21" s="11" t="s">
+      <c r="E30" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="K30" t="s">
+        <v>34</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="M30" t="s">
         <v>33</v>
       </c>
-      <c r="I21" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="K21" t="s">
-        <v>53</v>
-      </c>
-      <c r="L21" t="s">
-        <v>136</v>
-      </c>
-      <c r="M21" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="N21" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="O21" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="P21" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>188</v>
-      </c>
-      <c r="R21" s="13" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="22" spans="2:18">
-      <c r="B22" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" t="s">
-        <v>51</v>
-      </c>
-      <c r="E22" t="s">
-        <v>74</v>
-      </c>
-      <c r="F22" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" t="s">
-        <v>33</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="L22" t="s">
-        <v>134</v>
-      </c>
-      <c r="R22" s="13"/>
-    </row>
-    <row r="23" spans="2:18">
-      <c r="B23" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" t="s">
-        <v>73</v>
-      </c>
-      <c r="E23" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" t="s">
-        <v>37</v>
-      </c>
-      <c r="G23" t="s">
-        <v>37</v>
-      </c>
-      <c r="H23" t="s">
-        <v>37</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J23" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="K23" t="s">
+      <c r="N30" t="s">
+        <v>138</v>
+      </c>
+      <c r="O30" t="s">
+        <v>148</v>
+      </c>
+      <c r="P30" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q30" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="R30" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" hidden="1">
+      <c r="A31" t="s">
+        <v>200</v>
+      </c>
+      <c r="B31" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" t="s">
         <v>72</v>
       </c>
-      <c r="L23" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="24" spans="2:18">
-      <c r="B24" t="s">
-        <v>75</v>
-      </c>
-      <c r="C24" t="s">
-        <v>73</v>
-      </c>
-      <c r="E24" t="s">
-        <v>74</v>
-      </c>
-      <c r="F24" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" t="s">
-        <v>37</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J24" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="K24" t="s">
-        <v>76</v>
-      </c>
-      <c r="L24" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="25" spans="2:18">
-      <c r="B25" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" t="s">
-        <v>73</v>
-      </c>
-      <c r="E25" t="s">
-        <v>74</v>
-      </c>
-      <c r="F25" t="s">
-        <v>23</v>
-      </c>
-      <c r="G25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" t="s">
-        <v>37</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J25" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="K25" t="s">
-        <v>78</v>
-      </c>
-      <c r="L25" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="26" spans="2:18">
-      <c r="B26" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" t="s">
-        <v>21</v>
-      </c>
-      <c r="D26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" t="s">
-        <v>23</v>
-      </c>
-      <c r="G26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" t="s">
-        <v>37</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J26" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="K26" t="s">
-        <v>20</v>
-      </c>
-      <c r="L26" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="27" spans="2:18">
-      <c r="B27" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D27" t="s">
-        <v>19</v>
-      </c>
-      <c r="E27" t="s">
-        <v>26</v>
-      </c>
-      <c r="F27" t="s">
-        <v>23</v>
-      </c>
-      <c r="G27" t="s">
-        <v>23</v>
-      </c>
-      <c r="H27" t="s">
-        <v>37</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L27" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="28" spans="2:18">
-      <c r="B28" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D28" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" t="s">
-        <v>22</v>
-      </c>
-      <c r="F28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H28" t="s">
-        <v>37</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J28" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="K28" t="s">
-        <v>29</v>
-      </c>
-      <c r="L28" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="29" spans="2:18">
-      <c r="B29" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="H29" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J29" s="10" t="s">
+      <c r="F31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" t="s">
+        <v>21</v>
+      </c>
+      <c r="H31" t="s">
+        <v>98</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="J31" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="K29" t="s">
-        <v>32</v>
-      </c>
-      <c r="L29" t="s">
-        <v>141</v>
-      </c>
-      <c r="M29" t="s">
-        <v>31</v>
-      </c>
-      <c r="N29" t="s">
-        <v>144</v>
-      </c>
-      <c r="O29" t="s">
-        <v>145</v>
-      </c>
-      <c r="P29" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q29" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="R29" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="30" spans="2:18">
-      <c r="B30" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="H30" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J30" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="K30" t="s">
-        <v>36</v>
-      </c>
-      <c r="L30" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="M30" t="s">
-        <v>35</v>
-      </c>
-      <c r="N30" t="s">
-        <v>140</v>
-      </c>
-      <c r="O30" t="s">
-        <v>150</v>
-      </c>
-      <c r="P30" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q30" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="R30" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="31" spans="2:18">
-      <c r="B31" t="s">
-        <v>85</v>
-      </c>
-      <c r="C31" t="s">
-        <v>15</v>
-      </c>
-      <c r="E31" t="s">
-        <v>74</v>
-      </c>
-      <c r="F31" t="s">
-        <v>23</v>
-      </c>
-      <c r="G31" t="s">
-        <v>23</v>
-      </c>
-      <c r="H31" t="s">
-        <v>100</v>
-      </c>
-      <c r="I31" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="J31" s="10" t="s">
-        <v>125</v>
-      </c>
       <c r="K31" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L31" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
